--- a/matlab/case1/outputs/results/CaseStudy_1_results.xlsx
+++ b/matlab/case1/outputs/results/CaseStudy_1_results.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="348" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="522" uniqueCount="64">
   <si>
     <t>Variable</t>
   </si>
@@ -166,6 +166,48 @@
   </si>
   <si>
     <t>VIF</t>
+  </si>
+  <si>
+    <t>65.30 +/- 6.63</t>
+  </si>
+  <si>
+    <t>96.10 +/- 11.15</t>
+  </si>
+  <si>
+    <t>0.70 +/- 0.13</t>
+  </si>
+  <si>
+    <t>31.95 +/- 9.30</t>
+  </si>
+  <si>
+    <t>21.73 +/- 6.00</t>
+  </si>
+  <si>
+    <t>426.25 +/- 19.48</t>
+  </si>
+  <si>
+    <t>400.63 +/- 57.50</t>
+  </si>
+  <si>
+    <t>[49.00, 82.00]</t>
+  </si>
+  <si>
+    <t>[74.00, 119.00]</t>
+  </si>
+  <si>
+    <t>[0.39, 0.93]</t>
+  </si>
+  <si>
+    <t>[3.00, 48.00]</t>
+  </si>
+  <si>
+    <t>[8.00, 30.00]</t>
+  </si>
+  <si>
+    <t>[397.00, 460.10]</t>
+  </si>
+  <si>
+    <t>[292.90, 553.70]</t>
   </si>
 </sst>
 </file>
@@ -242,10 +284,10 @@
         <v>40</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -270,10 +312,10 @@
         <v>40</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
@@ -284,10 +326,10 @@
         <v>40</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
@@ -298,10 +340,10 @@
         <v>40</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -312,10 +354,10 @@
         <v>40</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -340,10 +382,10 @@
         <v>40</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -368,10 +410,10 @@
         <v>40</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -415,10 +457,10 @@
         <v>2</v>
       </c>
       <c r="C2" s="0">
-        <v>-0.3276986272214048</v>
+        <v>-0.32076960650489139</v>
       </c>
       <c r="D2" s="0">
-        <v>0.038997615038326244</v>
+        <v>0.043583784601680553</v>
       </c>
       <c r="E2" s="0" t="b">
         <v>1</v>
@@ -432,10 +474,10 @@
         <v>3</v>
       </c>
       <c r="C3" s="0">
-        <v>-0.18830901822170465</v>
+        <v>0.028715825017509876</v>
       </c>
       <c r="D3" s="0">
-        <v>0.24456527473085909</v>
+        <v>0.86037882296411838</v>
       </c>
       <c r="E3" s="0" t="b">
         <v>0</v>
@@ -449,10 +491,10 @@
         <v>4</v>
       </c>
       <c r="C4" s="0">
-        <v>-0.71004827297892459</v>
+        <v>-0.44225737798787329</v>
       </c>
       <c r="D4" s="0">
-        <v>2.8782795722228808e-07</v>
+        <v>0.0042718176143901193</v>
       </c>
       <c r="E4" s="0" t="b">
         <v>1</v>
@@ -466,13 +508,13 @@
         <v>5</v>
       </c>
       <c r="C5" s="0">
-        <v>-0.50585695940930708</v>
+        <v>-0.20633880309707095</v>
       </c>
       <c r="D5" s="0">
-        <v>0.00086868311973366046</v>
+        <v>0.20145465461205814</v>
       </c>
       <c r="E5" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -483,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="0">
-        <v>-0.28349159290371811</v>
+        <v>-0.23297194771013291</v>
       </c>
       <c r="D6" s="0">
-        <v>0.076283179664227596</v>
+        <v>0.14797700038895334</v>
       </c>
       <c r="E6" s="0" t="b">
         <v>0</v>
@@ -500,10 +542,10 @@
         <v>7</v>
       </c>
       <c r="C7" s="0">
-        <v>-0.11096265000192404</v>
+        <v>-0.10502922901817718</v>
       </c>
       <c r="D7" s="0">
-        <v>0.49546322803233034</v>
+        <v>0.51893556116976414</v>
       </c>
       <c r="E7" s="0" t="b">
         <v>0</v>
@@ -517,10 +559,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="0">
-        <v>0.18059396587324927</v>
+        <v>0.077562437063624284</v>
       </c>
       <c r="D8" s="0">
-        <v>0.26478285493805886</v>
+        <v>0.63428071255079377</v>
       </c>
       <c r="E8" s="0" t="b">
         <v>0</v>
@@ -534,10 +576,10 @@
         <v>9</v>
       </c>
       <c r="C9" s="0">
-        <v>0.15163060788656554</v>
+        <v>0.15718374308125166</v>
       </c>
       <c r="D9" s="0">
-        <v>0.35030267949551031</v>
+        <v>0.33272849168845919</v>
       </c>
       <c r="E9" s="0" t="b">
         <v>0</v>
@@ -551,10 +593,10 @@
         <v>10</v>
       </c>
       <c r="C10" s="0">
-        <v>0.50232220425344687</v>
+        <v>0.42648027310851783</v>
       </c>
       <c r="D10" s="0">
-        <v>0.00095691684828153089</v>
+        <v>0.0060660387163752414</v>
       </c>
       <c r="E10" s="0" t="b">
         <v>1</v>
@@ -568,13 +610,13 @@
         <v>3</v>
       </c>
       <c r="C11" s="0">
-        <v>0.31711375801899822</v>
+        <v>0.2497524343343927</v>
       </c>
       <c r="D11" s="0">
-        <v>0.046174196985041639</v>
+        <v>0.12012937352637365</v>
       </c>
       <c r="E11" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -585,10 +627,10 @@
         <v>4</v>
       </c>
       <c r="C12" s="0">
-        <v>0.21174871838611914</v>
+        <v>0.10353794297916104</v>
       </c>
       <c r="D12" s="0">
-        <v>0.18962758734305452</v>
+        <v>0.52492044488951328</v>
       </c>
       <c r="E12" s="0" t="b">
         <v>0</v>
@@ -602,10 +644,10 @@
         <v>5</v>
       </c>
       <c r="C13" s="0">
-        <v>0.2413211843703934</v>
+        <v>0.17416271711687262</v>
       </c>
       <c r="D13" s="0">
-        <v>0.13358265919518908</v>
+        <v>0.28245806084927672</v>
       </c>
       <c r="E13" s="0" t="b">
         <v>0</v>
@@ -619,10 +661,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="0">
-        <v>0.23553551443614279</v>
+        <v>0.22348947469119684</v>
       </c>
       <c r="D14" s="0">
-        <v>0.14344142788871894</v>
+        <v>0.16566848424230007</v>
       </c>
       <c r="E14" s="0" t="b">
         <v>0</v>
@@ -636,10 +678,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="0">
-        <v>0.029207373423151869</v>
+        <v>0.029207373423151859</v>
       </c>
       <c r="D15" s="0">
-        <v>0.85801300445214601</v>
+        <v>0.85801300445214612</v>
       </c>
       <c r="E15" s="0" t="b">
         <v>0</v>
@@ -653,10 +695,10 @@
         <v>8</v>
       </c>
       <c r="C16" s="0">
-        <v>-0.046372457011057369</v>
+        <v>-0.00844938876332995</v>
       </c>
       <c r="D16" s="0">
-        <v>0.77630466622927397</v>
+        <v>0.95873191863705165</v>
       </c>
       <c r="E16" s="0" t="b">
         <v>0</v>
@@ -687,10 +729,10 @@
         <v>10</v>
       </c>
       <c r="C18" s="0">
-        <v>-0.3712959149202617</v>
+        <v>-0.35458821057559137</v>
       </c>
       <c r="D18" s="0">
-        <v>0.018332438803999519</v>
+        <v>0.024767838506101987</v>
       </c>
       <c r="E18" s="0" t="b">
         <v>1</v>
@@ -704,13 +746,13 @@
         <v>4</v>
       </c>
       <c r="C19" s="0">
-        <v>0.35673609029997017</v>
+        <v>0.22200468707082535</v>
       </c>
       <c r="D19" s="0">
-        <v>0.023847875205959657</v>
+        <v>0.16857131980100082</v>
       </c>
       <c r="E19" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -721,10 +763,10 @@
         <v>5</v>
       </c>
       <c r="C20" s="0">
-        <v>0.50361087337633237</v>
+        <v>0.55884482093071974</v>
       </c>
       <c r="D20" s="0">
-        <v>0.00092386767961060475</v>
+        <v>0.00017824264479593556</v>
       </c>
       <c r="E20" s="0" t="b">
         <v>1</v>
@@ -738,10 +780,10 @@
         <v>6</v>
       </c>
       <c r="C21" s="0">
-        <v>0.21857207698116418</v>
+        <v>0.16203217683041646</v>
       </c>
       <c r="D21" s="0">
-        <v>0.17542213195807732</v>
+        <v>0.31783999557333376</v>
       </c>
       <c r="E21" s="0" t="b">
         <v>0</v>
@@ -755,10 +797,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="0">
-        <v>0.035443013447599959</v>
+        <v>0.003327431726896291</v>
       </c>
       <c r="D22" s="0">
-        <v>0.82811385317635966</v>
+        <v>0.98374244274464862</v>
       </c>
       <c r="E22" s="0" t="b">
         <v>0</v>
@@ -772,10 +814,10 @@
         <v>8</v>
       </c>
       <c r="C23" s="0">
-        <v>-0.27066629927565378</v>
+        <v>-0.24240371107575703</v>
       </c>
       <c r="D23" s="0">
-        <v>0.09117025603824834</v>
+        <v>0.13179534224606926</v>
       </c>
       <c r="E23" s="0" t="b">
         <v>0</v>
@@ -789,13 +831,13 @@
         <v>9</v>
       </c>
       <c r="C24" s="0">
-        <v>-0.31375702173921066</v>
+        <v>-0.28546003313409529</v>
       </c>
       <c r="D24" s="0">
-        <v>0.048660912245744911</v>
+        <v>0.074177427812772506</v>
       </c>
       <c r="E24" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -806,10 +848,10 @@
         <v>10</v>
       </c>
       <c r="C25" s="0">
-        <v>-0.30331596855014764</v>
+        <v>-0.20946107072819323</v>
       </c>
       <c r="D25" s="0">
-        <v>0.057092577416314745</v>
+        <v>0.19456738968384302</v>
       </c>
       <c r="E25" s="0" t="b">
         <v>0</v>
@@ -823,13 +865,13 @@
         <v>5</v>
       </c>
       <c r="C26" s="0">
-        <v>0.44645641822750692</v>
+        <v>0.22590533842739186</v>
       </c>
       <c r="D26" s="0">
-        <v>0.0038803476272463409</v>
+        <v>0.16102278290369454</v>
       </c>
       <c r="E26" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -840,10 +882,10 @@
         <v>6</v>
       </c>
       <c r="C27" s="0">
-        <v>0.19362852106327597</v>
+        <v>0.079551266708134588</v>
       </c>
       <c r="D27" s="0">
-        <v>0.23124744677151332</v>
+        <v>0.62558752405906204</v>
       </c>
       <c r="E27" s="0" t="b">
         <v>0</v>
@@ -857,10 +899,10 @@
         <v>7</v>
       </c>
       <c r="C28" s="0">
-        <v>0.3450111807807596</v>
+        <v>0.40310559697843978</v>
       </c>
       <c r="D28" s="0">
-        <v>0.029236292304899734</v>
+        <v>0.0099063358367047129</v>
       </c>
       <c r="E28" s="0" t="b">
         <v>1</v>
@@ -874,10 +916,10 @@
         <v>8</v>
       </c>
       <c r="C29" s="0">
-        <v>-0.45962469321456845</v>
+        <v>-0.65139152034797143</v>
       </c>
       <c r="D29" s="0">
-        <v>0.0028480614966270752</v>
+        <v>5.3115403599495013e-06</v>
       </c>
       <c r="E29" s="0" t="b">
         <v>1</v>
@@ -891,10 +933,10 @@
         <v>9</v>
       </c>
       <c r="C30" s="0">
-        <v>-0.14159527401614058</v>
+        <v>-0.048804567455873152</v>
       </c>
       <c r="D30" s="0">
-        <v>0.38346324252051545</v>
+        <v>0.76489610015722842</v>
       </c>
       <c r="E30" s="0" t="b">
         <v>0</v>
@@ -908,10 +950,10 @@
         <v>10</v>
       </c>
       <c r="C31" s="0">
-        <v>-0.46861176465910909</v>
+        <v>-0.34348702726493546</v>
       </c>
       <c r="D31" s="0">
-        <v>0.0022898944675834492</v>
+        <v>0.030005326235047466</v>
       </c>
       <c r="E31" s="0" t="b">
         <v>1</v>
@@ -925,10 +967,10 @@
         <v>6</v>
       </c>
       <c r="C32" s="0">
-        <v>0.27846849262140377</v>
+        <v>0.20446330532115656</v>
       </c>
       <c r="D32" s="0">
-        <v>0.081868917546225606</v>
+        <v>0.20567283025392868</v>
       </c>
       <c r="E32" s="0" t="b">
         <v>0</v>
@@ -942,10 +984,10 @@
         <v>7</v>
       </c>
       <c r="C33" s="0">
-        <v>-0.036134522353380522</v>
+        <v>-0.08945870137830389</v>
       </c>
       <c r="D33" s="0">
-        <v>0.82481203335059061</v>
+        <v>0.58304108560161971</v>
       </c>
       <c r="E33" s="0" t="b">
         <v>0</v>
@@ -959,10 +1001,10 @@
         <v>8</v>
       </c>
       <c r="C34" s="0">
-        <v>-0.24457185102237977</v>
+        <v>-0.22442905419427286</v>
       </c>
       <c r="D34" s="0">
-        <v>0.12826919483789556</v>
+        <v>0.16385030920432297</v>
       </c>
       <c r="E34" s="0" t="b">
         <v>0</v>
@@ -976,10 +1018,10 @@
         <v>9</v>
       </c>
       <c r="C35" s="0">
-        <v>0.33017667963182412</v>
+        <v>0.37624862028608141</v>
       </c>
       <c r="D35" s="0">
-        <v>0.037456219508379719</v>
+        <v>0.016719758808152789</v>
       </c>
       <c r="E35" s="0" t="b">
         <v>1</v>
@@ -993,10 +1035,10 @@
         <v>10</v>
       </c>
       <c r="C36" s="0">
-        <v>-0.46271627560018624</v>
+        <v>-0.3435498800882304</v>
       </c>
       <c r="D36" s="0">
-        <v>0.0026439058676920898</v>
+        <v>0.029973286372505351</v>
       </c>
       <c r="E36" s="0" t="b">
         <v>1</v>
@@ -1010,10 +1052,10 @@
         <v>7</v>
       </c>
       <c r="C37" s="0">
-        <v>0.12271501997890941</v>
+        <v>0.11571569119083092</v>
       </c>
       <c r="D37" s="0">
-        <v>0.45062993698606957</v>
+        <v>0.47706108219202203</v>
       </c>
       <c r="E37" s="0" t="b">
         <v>0</v>
@@ -1027,10 +1069,10 @@
         <v>8</v>
       </c>
       <c r="C38" s="0">
-        <v>-0.010489029542418815</v>
+        <v>0.026688489599961947</v>
       </c>
       <c r="D38" s="0">
-        <v>0.94878187475365861</v>
+        <v>0.87014886905989464</v>
       </c>
       <c r="E38" s="0" t="b">
         <v>0</v>
@@ -1044,10 +1086,10 @@
         <v>9</v>
       </c>
       <c r="C39" s="0">
-        <v>-0.17374271031828453</v>
+        <v>-0.17303531646496131</v>
       </c>
       <c r="D39" s="0">
-        <v>0.28363846451128349</v>
+        <v>0.28563378987422272</v>
       </c>
       <c r="E39" s="0" t="b">
         <v>0</v>
@@ -1061,10 +1103,10 @@
         <v>10</v>
       </c>
       <c r="C40" s="0">
-        <v>-0.17779871719435064</v>
+        <v>-0.12567379295996656</v>
       </c>
       <c r="D40" s="0">
-        <v>0.27237305864703032</v>
+        <v>0.43970124087293638</v>
       </c>
       <c r="E40" s="0" t="b">
         <v>0</v>
@@ -1078,10 +1120,10 @@
         <v>8</v>
       </c>
       <c r="C41" s="0">
-        <v>-0.0060099284213208847</v>
+        <v>0.0068551517012041029</v>
       </c>
       <c r="D41" s="0">
-        <v>0.97064039711001271</v>
+        <v>0.96651351078264647</v>
       </c>
       <c r="E41" s="0" t="b">
         <v>0</v>
@@ -1095,7 +1137,7 @@
         <v>9</v>
       </c>
       <c r="C42" s="0">
-        <v>-0.13138725242585347</v>
+        <v>-0.13138725242585342</v>
       </c>
       <c r="D42" s="0">
         <v>0.419016804350133</v>
@@ -1112,10 +1154,10 @@
         <v>10</v>
       </c>
       <c r="C43" s="0">
-        <v>-0.28323438029638759</v>
+        <v>-0.28452104672909306</v>
       </c>
       <c r="D43" s="0">
-        <v>0.076561756332524461</v>
+        <v>0.075176154088091585</v>
       </c>
       <c r="E43" s="0" t="b">
         <v>0</v>
@@ -1129,10 +1171,10 @@
         <v>9</v>
       </c>
       <c r="C44" s="0">
-        <v>-0.12112915874195565</v>
+        <v>-0.13817526058988122</v>
       </c>
       <c r="D44" s="0">
-        <v>0.45654777233532973</v>
+        <v>0.39517213429167575</v>
       </c>
       <c r="E44" s="0" t="b">
         <v>0</v>
@@ -1146,10 +1188,10 @@
         <v>10</v>
       </c>
       <c r="C45" s="0">
-        <v>0.18518589698039875</v>
+        <v>0.13143996895161483</v>
       </c>
       <c r="D45" s="0">
-        <v>0.25262040653926732</v>
+        <v>0.41882855161098187</v>
       </c>
       <c r="E45" s="0" t="b">
         <v>0</v>
@@ -1163,10 +1205,10 @@
         <v>10</v>
       </c>
       <c r="C46" s="0">
-        <v>-0.012792214140413984</v>
+        <v>-0.027914886982842734</v>
       </c>
       <c r="D46" s="0">
-        <v>0.93755546348060548</v>
+        <v>0.86423630037578181</v>
       </c>
       <c r="E46" s="0" t="b">
         <v>0</v>
@@ -1187,7 +1229,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="true"/>
     <col min="5" max="5" width="15.7109375" customWidth="true"/>
     <col min="6" max="6" width="15.42578125" customWidth="true"/>
-    <col min="7" max="7" width="16.42578125" customWidth="true"/>
+    <col min="7" max="7" width="15.42578125" customWidth="true"/>
     <col min="8" max="8" width="15.5703125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -1225,19 +1267,19 @@
         <v>44</v>
       </c>
       <c r="C2" s="0">
-        <v>1.7627319133452983</v>
+        <v>2.733810686500822</v>
       </c>
       <c r="D2" s="0">
-        <v>0.20011286987575974</v>
+        <v>0.27556613371044619</v>
       </c>
       <c r="E2" s="0">
-        <v>1.6424689189568202e-10</v>
+        <v>7.6814736215726689e-12</v>
       </c>
       <c r="F2" s="0">
-        <v>1.3568842024312888</v>
+        <v>2.17493666384929</v>
       </c>
       <c r="G2" s="0">
-        <v>2.1685796242593076</v>
+        <v>3.2926847091523541</v>
       </c>
       <c r="H2" s="0" t="b">
         <v>1</v>
@@ -1251,19 +1293,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="0">
-        <v>-0.0055132702600252399</v>
+        <v>-0.0069353677394479764</v>
       </c>
       <c r="D3" s="0">
-        <v>0.00084549789676626049</v>
+        <v>0.0017569690699394923</v>
       </c>
       <c r="E3" s="0">
-        <v>1.4078307527032557e-07</v>
+        <v>0.00035146139782691883</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.0072280194722984794</v>
+        <v>-0.01049866617010046</v>
       </c>
       <c r="G3" s="0">
-        <v>-0.0037985210477520003</v>
+        <v>-0.0033720693087954932</v>
       </c>
       <c r="H3" s="0" t="b">
         <v>1</v>
@@ -1277,19 +1319,19 @@
         <v>7</v>
       </c>
       <c r="C4" s="0">
-        <v>0.023179982144959636</v>
+        <v>0.054845208743415141</v>
       </c>
       <c r="D4" s="0">
-        <v>0.0078601480458722617</v>
+        <v>0.013278574186239261</v>
       </c>
       <c r="E4" s="0">
-        <v>0.0055700517661435136</v>
+        <v>0.00020571948097734228</v>
       </c>
       <c r="F4" s="0">
-        <v>0.0072388630463079036</v>
+        <v>0.027915012094729449</v>
       </c>
       <c r="G4" s="0">
-        <v>0.039121101243611373</v>
+        <v>0.081775405392100833</v>
       </c>
       <c r="H4" s="0" t="b">
         <v>1</v>
@@ -1303,19 +1345,19 @@
         <v>8</v>
       </c>
       <c r="C5" s="0">
-        <v>-0.0017301359723671992</v>
+        <v>-0.0041681845826491114</v>
       </c>
       <c r="D5" s="0">
-        <v>0.00046949403579408231</v>
+        <v>0.0005947899755515333</v>
       </c>
       <c r="E5" s="0">
-        <v>0.00074726942415737183</v>
+        <v>3.2061299989872604e-08</v>
       </c>
       <c r="F5" s="0">
-        <v>-0.0026823140098572776</v>
+        <v>-0.0053744745639084839</v>
       </c>
       <c r="G5" s="0">
-        <v>-0.00077795793487712072</v>
+        <v>-0.0029618946013897389</v>
       </c>
       <c r="H5" s="0" t="b">
         <v>1</v>
@@ -1329,19 +1371,19 @@
         <v>44</v>
       </c>
       <c r="C6" s="0">
-        <v>-38.056536590147154</v>
+        <v>-51.652297834996617</v>
       </c>
       <c r="D6" s="0">
-        <v>47.028945433122658</v>
+        <v>27.623873752013328</v>
       </c>
       <c r="E6" s="0">
-        <v>0.42436763314050319</v>
+        <v>0.070678808275444122</v>
       </c>
       <c r="F6" s="0">
-        <v>-133.85136365064031</v>
+        <v>-107.92028735600482</v>
       </c>
       <c r="G6" s="0">
-        <v>57.738290470345994</v>
+        <v>4.6156916860115942</v>
       </c>
       <c r="H6" s="0" t="b">
         <v>0</v>
@@ -1355,19 +1397,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="0">
-        <v>-0.65809987672852366</v>
+        <v>-0.45526660608948105</v>
       </c>
       <c r="D7" s="0">
-        <v>0.14692163460814209</v>
+        <v>0.14982834567959527</v>
       </c>
       <c r="E7" s="0">
-        <v>8.9611698907107162e-05</v>
+        <v>0.0047061450086973815</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.95736945313750965</v>
+        <v>-0.76045695919971479</v>
       </c>
       <c r="G7" s="0">
-        <v>-0.35883030031953761</v>
+        <v>-0.15007625297924737</v>
       </c>
       <c r="H7" s="0" t="b">
         <v>1</v>
@@ -1381,19 +1423,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="0">
-        <v>-0.6761344601800735</v>
+        <v>-0.61894760541847671</v>
       </c>
       <c r="D8" s="0">
-        <v>2.2604485947830439</v>
+        <v>1.8750903489607695</v>
       </c>
       <c r="E8" s="0">
-        <v>0.76678624811277274</v>
+        <v>0.74348366821566092</v>
       </c>
       <c r="F8" s="0">
-        <v>-5.2805175740711849</v>
+        <v>-4.438381659216903</v>
       </c>
       <c r="G8" s="0">
-        <v>3.9282486537110377</v>
+        <v>3.2004864483799498</v>
       </c>
       <c r="H8" s="0" t="b">
         <v>0</v>
@@ -1407,19 +1449,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="0">
-        <v>0.61949210404785671</v>
+        <v>0.63950870190228692</v>
       </c>
       <c r="D9" s="0">
-        <v>0.10603527146464949</v>
+        <v>0.088217951630042826</v>
       </c>
       <c r="E9" s="0">
-        <v>1.7141498846858186e-06</v>
+        <v>3.0923278127928069e-08</v>
       </c>
       <c r="F9" s="0">
-        <v>0.4035053240186689</v>
+        <v>0.45981461473530238</v>
       </c>
       <c r="G9" s="0">
-        <v>0.83547888407704451</v>
+        <v>0.81920278906927146</v>
       </c>
       <c r="H9" s="0" t="b">
         <v>1</v>
@@ -1433,19 +1475,19 @@
         <v>7</v>
       </c>
       <c r="C10" s="0">
-        <v>-0.67829513206831082</v>
+        <v>-0.64179331475446988</v>
       </c>
       <c r="D10" s="0">
-        <v>1.2277575672387375</v>
+        <v>1.0222264276781186</v>
       </c>
       <c r="E10" s="0">
-        <v>0.58446732297070858</v>
+        <v>0.53456480213790303</v>
       </c>
       <c r="F10" s="0">
-        <v>-3.1791554584623514</v>
+        <v>-2.7240004098581343</v>
       </c>
       <c r="G10" s="0">
-        <v>1.8225651943257297</v>
+        <v>1.4404137803491945</v>
       </c>
       <c r="H10" s="0" t="b">
         <v>0</v>
@@ -1459,19 +1501,19 @@
         <v>8</v>
       </c>
       <c r="C11" s="0">
-        <v>0.070465151568127729</v>
+        <v>0.040214360508817777</v>
       </c>
       <c r="D11" s="0">
-        <v>0.073828826800940661</v>
+        <v>0.046040256988975362</v>
       </c>
       <c r="E11" s="0">
-        <v>0.34701605149618653</v>
+        <v>0.388919790581157</v>
       </c>
       <c r="F11" s="0">
-        <v>-0.079919247451248995</v>
+        <v>-0.053566574093498055</v>
       </c>
       <c r="G11" s="0">
-        <v>0.22084955058750444</v>
+        <v>0.13399529511113362</v>
       </c>
       <c r="H11" s="0" t="b">
         <v>0</v>
@@ -1485,19 +1527,19 @@
         <v>9</v>
       </c>
       <c r="C12" s="0">
-        <v>3.833713566546276</v>
+        <v>3.3762964801699749</v>
       </c>
       <c r="D12" s="0">
-        <v>0.64397114027815838</v>
+        <v>0.53688551863054823</v>
       </c>
       <c r="E12" s="0">
-        <v>1.2428034174920734e-06</v>
+        <v>4.7184147730528622e-07</v>
       </c>
       <c r="F12" s="0">
-        <v>2.5219872786876736</v>
+        <v>2.2826964656505426</v>
       </c>
       <c r="G12" s="0">
-        <v>5.1454398544048789</v>
+        <v>4.4698964946894071</v>
       </c>
       <c r="H12" s="0" t="b">
         <v>1</v>
@@ -1511,19 +1553,19 @@
         <v>10</v>
       </c>
       <c r="C13" s="0">
-        <v>-0.045956579325200739</v>
+        <v>-0.010822586202000327</v>
       </c>
       <c r="D13" s="0">
-        <v>0.073006939366428422</v>
+        <v>0.018268044919713487</v>
       </c>
       <c r="E13" s="0">
-        <v>0.53350214017709652</v>
+        <v>0.5577243468453732</v>
       </c>
       <c r="F13" s="0">
-        <v>-0.1946668484246486</v>
+        <v>-0.048033376018791617</v>
       </c>
       <c r="G13" s="0">
-        <v>0.10275368977424711</v>
+        <v>0.02638820361479096</v>
       </c>
       <c r="H13" s="0" t="b">
         <v>0</v>
@@ -1537,22 +1579,22 @@
         <v>44</v>
       </c>
       <c r="C14" s="0">
-        <v>-24.486517688514386</v>
+        <v>-39.836264060860991</v>
       </c>
       <c r="D14" s="0">
-        <v>15.38974612967387</v>
+        <v>12.396731475108595</v>
       </c>
       <c r="E14" s="0">
-        <v>0.12033300218540466</v>
+        <v>0.0027651798510649945</v>
       </c>
       <c r="F14" s="0">
-        <v>-55.698369490718044</v>
+        <v>-64.978000797294243</v>
       </c>
       <c r="G14" s="0">
-        <v>6.7253341136892715</v>
+        <v>-14.694527324427739</v>
       </c>
       <c r="H14" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1563,19 +1605,19 @@
         <v>1</v>
       </c>
       <c r="C15" s="0">
-        <v>-0.66792848390145465</v>
+        <v>-0.46156124976004914</v>
       </c>
       <c r="D15" s="0">
-        <v>0.12014827006382536</v>
+        <v>0.1234959243631264</v>
       </c>
       <c r="E15" s="0">
-        <v>2.6992807911156865e-06</v>
+        <v>0.00064367331869074923</v>
       </c>
       <c r="F15" s="0">
-        <v>-0.91160046964607777</v>
+        <v>-0.712022593106441</v>
       </c>
       <c r="G15" s="0">
-        <v>-0.42425649815683159</v>
+        <v>-0.21109990641365722</v>
       </c>
       <c r="H15" s="0" t="b">
         <v>1</v>
@@ -1589,19 +1631,19 @@
         <v>3</v>
       </c>
       <c r="C16" s="0">
-        <v>0.60333392744515857</v>
+        <v>0.62717761181512932</v>
       </c>
       <c r="D16" s="0">
-        <v>0.09120235041980243</v>
+        <v>0.075662520857982737</v>
       </c>
       <c r="E16" s="0">
-        <v>1.0549016168612804e-07</v>
+        <v>7.2462982324092687e-10</v>
       </c>
       <c r="F16" s="0">
-        <v>0.41836698768344049</v>
+        <v>0.47372690716399646</v>
       </c>
       <c r="G16" s="0">
-        <v>0.78830086720687664</v>
+        <v>0.78062831646626218</v>
       </c>
       <c r="H16" s="0" t="b">
         <v>1</v>
@@ -1615,19 +1657,19 @@
         <v>9</v>
       </c>
       <c r="C17" s="0">
-        <v>3.819684298962327</v>
+        <v>3.3781909082234369</v>
       </c>
       <c r="D17" s="0">
-        <v>0.58057049490468071</v>
+        <v>0.4825937831412454</v>
       </c>
       <c r="E17" s="0">
-        <v>1.1778015481257078e-07</v>
+        <v>3.2820947188868891e-08</v>
       </c>
       <c r="F17" s="0">
-        <v>2.6422327610998937</v>
+        <v>2.3994453517242174</v>
       </c>
       <c r="G17" s="0">
-        <v>4.9971358368247607</v>
+        <v>4.3569364647226561</v>
       </c>
       <c r="H17" s="0" t="b">
         <v>1</v>
@@ -1659,7 +1701,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="0">
-        <v>1.1202264694582069</v>
+        <v>1.1221592246264211</v>
       </c>
     </row>
     <row r="3">
@@ -1667,7 +1709,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="0">
-        <v>1.0470771454885359</v>
+        <v>1.0315679823014063</v>
       </c>
     </row>
     <row r="4">
@@ -1675,7 +1717,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>1.1347074514554116</v>
+        <v>1.0953375544898265</v>
       </c>
     </row>
   </sheetData>
